--- a/4_results_excel/summary_comparison_constant_vs_variable_rates.xlsx
+++ b/4_results_excel/summary_comparison_constant_vs_variable_rates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Battuto\Desktop\malenia\supplementary_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadik\My Drive\Operation\ocean\Prall_etal.DiscretePrediction.CommunicationsBiology\4_results_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF02D77-F3FE-44CF-A9D5-9095D51DB6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877DD830-3EA8-4B8E-BE55-B71AFA469687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -719,19 +719,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68053A4E-B426-4D02-A5F1-14665BC27170}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="131.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="131.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B1" s="15"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +739,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -747,72 +747,72 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -820,7 +820,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
@@ -828,7 +828,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -836,22 +836,22 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
@@ -859,7 +859,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>59</v>
       </c>
@@ -867,7 +867,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>60</v>
       </c>
@@ -875,17 +875,17 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>30</v>
       </c>
@@ -901,20 +901,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD44F911-1668-46D7-8E1E-8B1B07959405}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" customWidth="1"/>
-    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="0.81640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>48</v>
       </c>
@@ -927,7 +927,7 @@
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -983,7 +983,7 @@
         <v>1.4190599203797076</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>1.1019199413850633</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>1.0088569832942273</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>1.1204385552660452</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>1.0816089013274623</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>1.0522813998429705</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>1.3765292508567102</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>1.1019970830036385</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>1.0681369694935354</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>1.2641123525415643</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>1.0217157342364305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>1.0318601114558785</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>17</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>49</v>
       </c>
@@ -1362,38 +1362,38 @@
         <v>1.1373764335902696</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="14">
-        <f>2*_xlfn.STDEV.S(C3:C14)/COUNT(C3:C14)</f>
-        <v>1.2757053901368616E-2</v>
+        <f>2*_xlfn.STDEV.S(C3:C14)/SQRT(COUNT(C3:C14))</f>
+        <v>4.4191731024130418E-2</v>
       </c>
       <c r="D17" s="14">
-        <f t="shared" ref="D17:I17" si="3">2*_xlfn.STDEV.S(D3:D14)/COUNT(D3:D14)</f>
-        <v>1.3112823034958263E-2</v>
+        <f t="shared" ref="D17:E17" si="3">2*_xlfn.STDEV.S(D3:D14)/SQRT(COUNT(D3:D14))</f>
+        <v>4.5424151454414474E-2</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="3"/>
-        <v>2.2319232696222987E-3</v>
+        <v>7.7316090031621437E-3</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="14">
-        <f t="shared" si="3"/>
-        <v>2.8626119229805857E-2</v>
+        <f>2*_xlfn.STDEV.S(G3:G14)/SQRT(COUNT(G3:G14))</f>
+        <v>9.9163785859096409E-2</v>
       </c>
       <c r="H17" s="14">
-        <f t="shared" si="3"/>
-        <v>2.7952248556237541E-2</v>
+        <f t="shared" ref="H17:I17" si="4">2*_xlfn.STDEV.S(H3:H14)/SQRT(COUNT(H3:H14))</f>
+        <v>9.6829429370394446E-2</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="3"/>
-        <v>2.3114287277101447E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>8.007023988936518E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
@@ -1406,7 +1406,7 @@
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>1.5980601721356418</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>0.74199999999999999</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" ref="E22:E33" si="4">C22-D22</f>
+        <f t="shared" ref="E22:E33" si="5">C22-D22</f>
         <v>3.1000000000000028E-2</v>
       </c>
       <c r="F22" s="10"/>
@@ -1487,11 +1487,11 @@
         <v>0.36600429913378352</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I33" si="5">H22/G22</f>
+        <f t="shared" ref="I22:I33" si="6">H22/G22</f>
         <v>1.3272879474894494</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>0.65</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8000000000000016E-2</v>
       </c>
       <c r="F23" s="10"/>
@@ -1516,11 +1516,11 @@
         <v>0.59874691911411348</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0956974098588574</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0.81599999999999995</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.200000000000002E-2</v>
       </c>
       <c r="F24" s="10"/>
@@ -1545,11 +1545,11 @@
         <v>0.19662352672783301</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.5245634288317613</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>0.88600000000000001</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-2.9000000000000026E-2</v>
       </c>
       <c r="F25" s="10"/>
@@ -1574,11 +1574,11 @@
         <v>0.11372892225388301</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0409289564840969</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>0.71499999999999997</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.7000000000000024E-2</v>
       </c>
       <c r="F26" s="10"/>
@@ -1603,11 +1603,11 @@
         <v>0.376877651256252</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1049445967849936</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>0.82699999999999996</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.6000000000000041E-2</v>
       </c>
       <c r="F27" s="10"/>
@@ -1632,11 +1632,11 @@
         <v>0.12669765304595801</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4622141959932582</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>0.75600000000000001</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.9000000000000035E-2</v>
       </c>
       <c r="F28" s="10"/>
@@ -1661,11 +1661,11 @@
         <v>0.327116141697188</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.376617753064578</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>0.72599999999999998</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.9000000000000017E-2</v>
       </c>
       <c r="F29" s="10"/>
@@ -1690,11 +1690,11 @@
         <v>0.43928075753207396</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0381941589373962</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>0.878</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.7000000000000024E-2</v>
       </c>
       <c r="F30" s="10"/>
@@ -1719,11 +1719,11 @@
         <v>7.8502374405082356E-2</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4141333489881094</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>0.83799999999999997</v>
       </c>
       <c r="E31" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8000000000000016E-2</v>
       </c>
       <c r="F31" s="10"/>
@@ -1748,11 +1748,11 @@
         <v>0.15665381004537701</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2419984621963118</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.7000000000000033E-2</v>
       </c>
       <c r="F32" s="10"/>
@@ -1777,11 +1777,11 @@
         <v>0.23572313467537298</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1522976642925571</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>17</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>0.51700000000000002</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F33" s="10"/>
@@ -1806,11 +1806,11 @@
         <v>0.68915515929040805</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>49</v>
       </c>
@@ -1820,59 +1820,59 @@
         <v>0.80958333333333332</v>
       </c>
       <c r="D34" s="14">
-        <f t="shared" ref="D34:E34" si="6">AVERAGE(D21:D32)</f>
+        <f t="shared" ref="D34:E34" si="7">AVERAGE(D21:D32)</f>
         <v>0.78841666666666665</v>
       </c>
       <c r="E34" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.1166666666666684E-2</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="14">
-        <f t="shared" ref="G34:I34" si="7">AVERAGE(G21:G32)</f>
+        <f t="shared" ref="G34:I34" si="8">AVERAGE(G21:G32)</f>
         <v>0.21730744649284639</v>
       </c>
       <c r="H34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.26099396031421312</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2814115079214174</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="14">
-        <f>2*_xlfn.STDEV.S(C21:C32)/COUNT(C21:C32)</f>
-        <v>1.2620821807538646E-2</v>
+        <f>2*_xlfn.STDEV.S(C21:C32)/SQRT(COUNT(C21:C32))</f>
+        <v>4.3719809207860422E-2</v>
       </c>
       <c r="D35" s="14">
-        <f t="shared" ref="D35:E35" si="8">2*_xlfn.STDEV.S(D21:D32)/COUNT(D21:D32)</f>
-        <v>1.2295695710151296E-2</v>
+        <f t="shared" ref="D35:E35" si="9">2*_xlfn.STDEV.S(D21:D32)/SQRT(COUNT(D21:D32))</f>
+        <v>4.2593539368777467E-2</v>
       </c>
       <c r="E35" s="14">
-        <f t="shared" si="8"/>
-        <v>3.8110904967490339E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.3202004745224476E-2</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="14">
-        <f t="shared" ref="G35:I35" si="9">2*_xlfn.STDEV.S(G21:G32)/COUNT(G21:G32)</f>
-        <v>2.5721731571531663E-2</v>
+        <f>2*_xlfn.STDEV.S(G21:G32)/SQRT(COUNT(G21:G32))</f>
+        <v>8.9102691881082607E-2</v>
       </c>
       <c r="H35" s="14">
-        <f t="shared" si="9"/>
-        <v>2.6799741920972651E-2</v>
+        <f t="shared" ref="H35:I35" si="10">2*_xlfn.STDEV.S(H21:H32)/SQRT(COUNT(H21:H32))</f>
+        <v>9.2837029273716357E-2</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="9"/>
-        <v>3.2632922245324041E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+        <f t="shared" si="10"/>
+        <v>0.11304375865669178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>54</v>
       </c>
@@ -1885,7 +1885,7 @@
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>0</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1.458227890049576</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>2</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>0.93200000000000005</v>
       </c>
       <c r="E40" s="10">
-        <f t="shared" ref="E40:E51" si="10">C40-D40</f>
+        <f t="shared" ref="E40:E51" si="11">C40-D40</f>
         <v>-8.0000000000000071E-3</v>
       </c>
       <c r="F40" s="10"/>
@@ -1966,11 +1966,11 @@
         <v>5.0241216436746797E-2</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40:I51" si="11">H40/G40</f>
+        <f t="shared" ref="I40:I51" si="12">H40/G40</f>
         <v>1.4972000040934601</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>0.86299999999999999</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2000000000000011E-2</v>
       </c>
       <c r="F41" s="10"/>
@@ -1995,11 +1995,11 @@
         <v>0.121038328377056</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4707815952233001</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0.93200000000000005</v>
       </c>
       <c r="E42" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5999999999999903E-2</v>
       </c>
       <c r="F42" s="10"/>
@@ -2024,11 +2024,11 @@
         <v>3.3556783528842803E-2</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.181598747653041</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>0.93400000000000005</v>
       </c>
       <c r="E43" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.9999999999998925E-3</v>
       </c>
       <c r="F43" s="10"/>
@@ -2053,11 +2053,11 @@
         <v>3.4591444769619097E-2</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1356646356273385</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>0.89500000000000002</v>
       </c>
       <c r="E44" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="F44" s="10"/>
@@ -2082,11 +2082,11 @@
         <v>7.1496001705069895E-2</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3658225194262954</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>0.96</v>
       </c>
       <c r="E45" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7000000000000015E-2</v>
       </c>
       <c r="F45" s="10"/>
@@ -2111,11 +2111,11 @@
         <v>1.51136378100482E-2</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.6717248845708239</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>0.91900000000000004</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.0000000000000044E-3</v>
       </c>
       <c r="F46" s="10"/>
@@ -2140,11 +2140,11 @@
         <v>4.1864204098698898E-2</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1418345500697056</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>0.86</v>
       </c>
       <c r="E47" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3000000000000012E-2</v>
       </c>
       <c r="F47" s="10"/>
@@ -2169,11 +2169,11 @@
         <v>9.4310679471241304E-2</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1460040258255875</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>0.95699999999999996</v>
       </c>
       <c r="E48" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.0000000000000009E-3</v>
       </c>
       <c r="F48" s="10"/>
@@ -2198,11 +2198,11 @@
         <v>1.4098924379501601E-2</v>
       </c>
       <c r="I48" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1678467186023507</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>0.92800000000000005</v>
       </c>
       <c r="E49" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.0000000000000071E-3</v>
       </c>
       <c r="F49" s="10"/>
@@ -2227,11 +2227,11 @@
         <v>3.7182925777801495E-2</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4114394391307248</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>0.89400000000000002</v>
       </c>
       <c r="E50" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2000000000000028E-2</v>
       </c>
       <c r="F50" s="10"/>
@@ -2256,11 +2256,11 @@
         <v>4.7091607533850603E-2</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.1684847134706122</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>17</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0.504</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F51" s="10"/>
@@ -2285,11 +2285,11 @@
         <v>0.69114917789727204</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
         <v>49</v>
       </c>
@@ -2299,69 +2299,69 @@
         <v>0.93058333333333332</v>
       </c>
       <c r="D52" s="14">
-        <f t="shared" ref="D52:E52" si="12">AVERAGE(D39:D50)</f>
+        <f t="shared" ref="D52:E52" si="13">AVERAGE(D39:D50)</f>
         <v>0.92041666666666666</v>
       </c>
       <c r="E52" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0166666666666657E-2</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="14">
-        <f t="shared" ref="G52:I52" si="13">AVERAGE(G39:G50)</f>
+        <f t="shared" ref="G52:I52" si="14">AVERAGE(G39:G50)</f>
         <v>3.7069674715350463E-2</v>
       </c>
       <c r="H52" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8059594651530028E-2</v>
       </c>
       <c r="I52" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.318052476978568</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="14">
-        <f>2*_xlfn.STDEV.S(C39:C50)/COUNT(C39:C50)</f>
-        <v>5.2505210579971351E-3</v>
+        <f>2*_xlfn.STDEV.S(C39:C50)/SQRT(COUNT(C39:C50))</f>
+        <v>1.8188338477322669E-2</v>
       </c>
       <c r="D53" s="14">
-        <f t="shared" ref="D53:E53" si="14">2*_xlfn.STDEV.S(D39:D50)/COUNT(D39:D50)</f>
-        <v>6.0022968387166038E-3</v>
+        <f t="shared" ref="D53:E53" si="15">2*_xlfn.STDEV.S(D39:D50)/SQRT(COUNT(D39:D50))</f>
+        <v>2.0792566173534428E-2</v>
       </c>
       <c r="E53" s="14">
-        <f t="shared" si="14"/>
-        <v>2.1007854872165488E-3</v>
+        <f t="shared" si="15"/>
+        <v>7.2773343993248014E-3</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="14">
-        <f t="shared" ref="G53:I53" si="15">2*_xlfn.STDEV.S(G39:G50)/COUNT(G39:G50)</f>
-        <v>4.10342146539592E-3</v>
+        <f>2*_xlfn.STDEV.S(G39:G50)/SQRT(COUNT(G39:G50))</f>
+        <v>1.421466892586894E-2</v>
       </c>
       <c r="H53" s="14">
-        <f t="shared" si="15"/>
-        <v>5.4649316202166386E-3</v>
+        <f t="shared" ref="H53:I53" si="16">2*_xlfn.STDEV.S(H39:H50)/SQRT(COUNT(H39:H50))</f>
+        <v>1.8931078452209846E-2</v>
       </c>
       <c r="I53" s="14">
-        <f t="shared" si="15"/>
-        <v>3.0510268927297374E-2</v>
+        <f t="shared" si="16"/>
+        <v>0.10569067186933809</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:D15">
     <cfRule type="colorScale" priority="99">
@@ -2797,7 +2797,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C16:I17 C34:I35 C52:I53" formulaRange="1"/>
+    <ignoredError sqref="C16:I16 C34:I34 C52:I52 F17 C17:E17 G17 H17:I17 C35 F35 D35:E35 G35:I35 C53:D53 F53 G53:H53" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>